--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azs1\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-kk_29knp\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B28CC7-C01B-4BB9-954D-C2C3DAC4A675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C32AF4-610C-4D11-A36D-8C627F83C726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3645" yWindow="-13320" windowWidth="5970" windowHeight="10455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3118" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3118" uniqueCount="239">
   <si>
     <t>示例客户：跨订阅VM规格建议与预计节省</t>
   </si>
@@ -549,13 +549,16 @@
     <t>Standard_E2s_v5</t>
   </si>
   <si>
+    <t>CPU核数减半，内存容量不变；平均用量和VM磁盘性能满足要求，列表价更低；9月该机器 100% 的费用由 RI/SP 覆盖：降配不会直接减少预付费用，需先交换预留或调整覆盖范围，节省在此之后才能实现</t>
+  </si>
+  <si>
+    <t>shop-web-02</t>
+  </si>
+  <si>
+    <t>shop-web-03</t>
+  </si>
+  <si>
     <t>CPU核数减半，内存容量不变；平均用量和VM磁盘性能满足要求，列表价更低</t>
-  </si>
-  <si>
-    <t>shop-web-02</t>
-  </si>
-  <si>
-    <t>shop-web-03</t>
   </si>
   <si>
     <t>shop-web-04</t>
@@ -1051,7 +1054,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-08A5-473A-B439-19D3B6023F0B}"/>
+              <c16:uniqueId val="{00000000-C71D-454C-A174-2F475DD86964}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1151,7 +1154,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-08A5-473A-B439-19D3B6023F0B}"/>
+              <c16:uniqueId val="{00000001-C71D-454C-A174-2F475DD86964}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1275,7 +1278,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-5FC0-4AF5-B94F-7F9DE7214013}"/>
+                <c16:uniqueId val="{00000001-A592-4410-8E57-7E0DDEF470C3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1285,7 +1288,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5FC0-4AF5-B94F-7F9DE7214013}"/>
+                <c16:uniqueId val="{00000003-A592-4410-8E57-7E0DDEF470C3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1295,7 +1298,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5FC0-4AF5-B94F-7F9DE7214013}"/>
+                <c16:uniqueId val="{00000005-A592-4410-8E57-7E0DDEF470C3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1351,7 +1354,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-5FC0-4AF5-B94F-7F9DE7214013}"/>
+              <c16:uniqueId val="{00000006-A592-4410-8E57-7E0DDEF470C3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1506,7 +1509,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0323-44D9-BC47-3CFF5CBFFB7F}"/>
+              <c16:uniqueId val="{00000000-FD32-43C4-B2C6-9453C50DB88A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1626,7 +1629,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-874A-46FA-BD9E-EB7D58CE7E1D}"/>
+                <c16:uniqueId val="{00000001-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1636,7 +1639,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-874A-46FA-BD9E-EB7D58CE7E1D}"/>
+                <c16:uniqueId val="{00000003-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1646,7 +1649,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-874A-46FA-BD9E-EB7D58CE7E1D}"/>
+                <c16:uniqueId val="{00000005-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1656,7 +1659,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-874A-46FA-BD9E-EB7D58CE7E1D}"/>
+                <c16:uniqueId val="{00000007-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1666,7 +1669,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-874A-46FA-BD9E-EB7D58CE7E1D}"/>
+                <c16:uniqueId val="{00000009-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1676,7 +1679,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-874A-46FA-BD9E-EB7D58CE7E1D}"/>
+                <c16:uniqueId val="{0000000B-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1750,7 +1753,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-874A-46FA-BD9E-EB7D58CE7E1D}"/>
+              <c16:uniqueId val="{0000000C-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5091,7 +5094,7 @@
         <v>56.94（省 123.88）</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AA13" s="2" t="s">
         <v>104</v>
@@ -5105,7 +5108,7 @@
         <v>157</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>154</v>
@@ -5179,7 +5182,7 @@
         <v>56.94（省 123.88）</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AA14" s="4" t="s">
         <v>105</v>
@@ -5190,10 +5193,10 @@
         <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>154</v>
@@ -5205,7 +5208,7 @@
         <v>155</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>60</v>
@@ -5278,16 +5281,16 @@
         <v>67</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>154</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>155</v>
@@ -5327,7 +5330,7 @@
         <v>108</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA16" s="4" t="s">
         <v>107</v>
@@ -5364,7 +5367,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -5377,7 +5380,7 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -5393,19 +5396,19 @@
         <v>63</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>22</v>
@@ -5414,7 +5417,7 @@
         <v>4</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -5441,15 +5444,15 @@
         <v>183.96</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B5" s="6">
         <v>0</v>
@@ -5471,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -5501,15 +5504,15 @@
         <v>0</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B7" s="6">
         <v>0</v>
@@ -5531,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -5561,10 +5564,10 @@
         <v>486.10700000000008</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -5591,10 +5594,10 @@
         <v>90.447000000000003</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -5625,7 +5628,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -5637,7 +5640,7 @@
     </row>
     <row r="2" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -5658,16 +5661,16 @@
         <v>116</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>79</v>
@@ -5684,10 +5687,10 @@
         <v>161</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F4" s="5">
         <v>6.3049999999999997</v>
@@ -5710,10 +5713,10 @@
         <v>161</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F5" s="6">
         <v>6.5</v>
@@ -5736,10 +5739,10 @@
         <v>161</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F6" s="5">
         <v>6.6950000000000003</v>
@@ -5762,10 +5765,10 @@
         <v>161</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F7" s="6">
         <v>6.3049999999999997</v>
@@ -5788,10 +5791,10 @@
         <v>161</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F8" s="5">
         <v>6.5</v>
@@ -5814,10 +5817,10 @@
         <v>161</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F9" s="6">
         <v>6.6950000000000003</v>
@@ -5840,10 +5843,10 @@
         <v>161</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F10" s="5">
         <v>6.3049999999999997</v>
@@ -5866,10 +5869,10 @@
         <v>161</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F11" s="6">
         <v>69.84</v>
@@ -5892,10 +5895,10 @@
         <v>161</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F12" s="5">
         <v>72</v>
@@ -5918,10 +5921,10 @@
         <v>161</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F13" s="6">
         <v>74.16</v>
@@ -5944,10 +5947,10 @@
         <v>161</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F14" s="5">
         <v>69.84</v>
@@ -5970,10 +5973,10 @@
         <v>161</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F15" s="6">
         <v>72</v>
@@ -5996,10 +5999,10 @@
         <v>161</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F16" s="5">
         <v>74.16</v>
@@ -6022,10 +6025,10 @@
         <v>161</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F17" s="6">
         <v>69.84</v>
@@ -6048,10 +6051,10 @@
         <v>161</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F18" s="5">
         <v>3.88</v>
@@ -6074,10 +6077,10 @@
         <v>161</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F19" s="6">
         <v>4</v>
@@ -6100,10 +6103,10 @@
         <v>161</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F20" s="5">
         <v>4.12</v>
@@ -6126,10 +6129,10 @@
         <v>161</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F21" s="6">
         <v>3.88</v>
@@ -6152,10 +6155,10 @@
         <v>161</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F22" s="5">
         <v>4</v>
@@ -6178,10 +6181,10 @@
         <v>161</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F23" s="6">
         <v>4.12</v>
@@ -6204,10 +6207,10 @@
         <v>161</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F24" s="5">
         <v>3.88</v>
@@ -6230,10 +6233,10 @@
         <v>161</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F25" s="6">
         <v>5.82</v>
@@ -6256,10 +6259,10 @@
         <v>161</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F26" s="5">
         <v>6</v>
@@ -6282,10 +6285,10 @@
         <v>161</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F27" s="6">
         <v>6.18</v>
@@ -6308,10 +6311,10 @@
         <v>161</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F28" s="5">
         <v>5.82</v>
@@ -6334,10 +6337,10 @@
         <v>161</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F29" s="6">
         <v>6</v>
@@ -6360,10 +6363,10 @@
         <v>161</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F30" s="5">
         <v>6.18</v>
@@ -6386,10 +6389,10 @@
         <v>161</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F31" s="6">
         <v>5.82</v>
@@ -6412,10 +6415,10 @@
         <v>161</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F32" s="5">
         <v>2.91</v>
@@ -6438,10 +6441,10 @@
         <v>161</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F33" s="6">
         <v>3</v>
@@ -6464,10 +6467,10 @@
         <v>161</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F34" s="5">
         <v>3.09</v>
@@ -6490,10 +6493,10 @@
         <v>161</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F35" s="6">
         <v>2.91</v>
@@ -6516,10 +6519,10 @@
         <v>161</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F36" s="5">
         <v>3</v>
@@ -6542,10 +6545,10 @@
         <v>161</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F37" s="6">
         <v>3.09</v>
@@ -6568,10 +6571,10 @@
         <v>161</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F38" s="5">
         <v>2.91</v>
@@ -6594,10 +6597,10 @@
         <v>161</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F39" s="6">
         <v>1.94</v>
@@ -6620,10 +6623,10 @@
         <v>161</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F40" s="5">
         <v>2</v>
@@ -6646,10 +6649,10 @@
         <v>161</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F41" s="6">
         <v>2.06</v>
@@ -6672,10 +6675,10 @@
         <v>161</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F42" s="5">
         <v>1.94</v>
@@ -6698,10 +6701,10 @@
         <v>161</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F43" s="6">
         <v>2</v>
@@ -6724,10 +6727,10 @@
         <v>161</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F44" s="5">
         <v>2.06</v>
@@ -6750,10 +6753,10 @@
         <v>161</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F45" s="6">
         <v>1.94</v>
@@ -6776,10 +6779,10 @@
         <v>164</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F46" s="5">
         <v>6.8869999999999996</v>
@@ -6802,10 +6805,10 @@
         <v>164</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F47" s="6">
         <v>7.1</v>
@@ -6828,10 +6831,10 @@
         <v>164</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F48" s="5">
         <v>7.3129999999999997</v>
@@ -6854,10 +6857,10 @@
         <v>164</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F49" s="6">
         <v>6.8869999999999996</v>
@@ -6880,10 +6883,10 @@
         <v>164</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F50" s="5">
         <v>7.1</v>
@@ -6906,10 +6909,10 @@
         <v>164</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F51" s="6">
         <v>7.3129999999999997</v>
@@ -6932,10 +6935,10 @@
         <v>164</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F52" s="5">
         <v>6.8869999999999996</v>
@@ -6958,10 +6961,10 @@
         <v>164</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F53" s="6">
         <v>67.900000000000006</v>
@@ -6984,10 +6987,10 @@
         <v>164</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F54" s="5">
         <v>70</v>
@@ -7010,10 +7013,10 @@
         <v>164</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F55" s="6">
         <v>72.099999999999994</v>
@@ -7036,10 +7039,10 @@
         <v>164</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F56" s="5">
         <v>67.900000000000006</v>
@@ -7062,10 +7065,10 @@
         <v>164</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F57" s="6">
         <v>70</v>
@@ -7088,10 +7091,10 @@
         <v>164</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F58" s="5">
         <v>72.099999999999994</v>
@@ -7114,10 +7117,10 @@
         <v>164</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F59" s="6">
         <v>67.900000000000006</v>
@@ -7140,10 +7143,10 @@
         <v>164</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F60" s="5">
         <v>3.88</v>
@@ -7166,10 +7169,10 @@
         <v>164</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F61" s="6">
         <v>4</v>
@@ -7192,10 +7195,10 @@
         <v>164</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F62" s="5">
         <v>4.12</v>
@@ -7218,10 +7221,10 @@
         <v>164</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F63" s="6">
         <v>3.88</v>
@@ -7244,10 +7247,10 @@
         <v>164</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F64" s="5">
         <v>4</v>
@@ -7270,10 +7273,10 @@
         <v>164</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F65" s="6">
         <v>4.12</v>
@@ -7296,10 +7299,10 @@
         <v>164</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F66" s="5">
         <v>3.88</v>
@@ -7322,10 +7325,10 @@
         <v>164</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F67" s="6">
         <v>5.82</v>
@@ -7348,10 +7351,10 @@
         <v>164</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F68" s="5">
         <v>6</v>
@@ -7374,10 +7377,10 @@
         <v>164</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F69" s="6">
         <v>6.18</v>
@@ -7400,10 +7403,10 @@
         <v>164</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F70" s="5">
         <v>5.82</v>
@@ -7426,10 +7429,10 @@
         <v>164</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F71" s="6">
         <v>6</v>
@@ -7452,10 +7455,10 @@
         <v>164</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F72" s="5">
         <v>6.18</v>
@@ -7478,10 +7481,10 @@
         <v>164</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F73" s="6">
         <v>5.82</v>
@@ -7504,10 +7507,10 @@
         <v>164</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F74" s="5">
         <v>2.91</v>
@@ -7530,10 +7533,10 @@
         <v>164</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F75" s="6">
         <v>3</v>
@@ -7556,10 +7559,10 @@
         <v>164</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F76" s="5">
         <v>3.09</v>
@@ -7582,10 +7585,10 @@
         <v>164</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F77" s="6">
         <v>2.91</v>
@@ -7608,10 +7611,10 @@
         <v>164</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F78" s="5">
         <v>3</v>
@@ -7634,10 +7637,10 @@
         <v>164</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F79" s="6">
         <v>3.09</v>
@@ -7660,10 +7663,10 @@
         <v>164</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F80" s="5">
         <v>2.91</v>
@@ -7686,10 +7689,10 @@
         <v>164</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F81" s="6">
         <v>1.94</v>
@@ -7712,10 +7715,10 @@
         <v>164</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F82" s="5">
         <v>2</v>
@@ -7738,10 +7741,10 @@
         <v>164</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F83" s="6">
         <v>2.06</v>
@@ -7764,10 +7767,10 @@
         <v>164</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F84" s="5">
         <v>1.94</v>
@@ -7790,10 +7793,10 @@
         <v>164</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F85" s="6">
         <v>2</v>
@@ -7816,10 +7819,10 @@
         <v>164</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F86" s="5">
         <v>2.06</v>
@@ -7842,10 +7845,10 @@
         <v>164</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F87" s="6">
         <v>1.94</v>
@@ -7868,10 +7871,10 @@
         <v>165</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F88" s="5">
         <v>6.0140000000000002</v>
@@ -7894,10 +7897,10 @@
         <v>165</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F89" s="6">
         <v>6.2</v>
@@ -7920,10 +7923,10 @@
         <v>165</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F90" s="5">
         <v>6.3860000000000001</v>
@@ -7946,10 +7949,10 @@
         <v>165</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F91" s="6">
         <v>6.0140000000000002</v>
@@ -7972,10 +7975,10 @@
         <v>165</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F92" s="5">
         <v>6.2</v>
@@ -7998,10 +8001,10 @@
         <v>165</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F93" s="6">
         <v>6.3860000000000001</v>
@@ -8024,10 +8027,10 @@
         <v>165</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F94" s="5">
         <v>6.0140000000000002</v>
@@ -8050,10 +8053,10 @@
         <v>165</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F95" s="6">
         <v>68.87</v>
@@ -8076,10 +8079,10 @@
         <v>165</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F96" s="5">
         <v>71</v>
@@ -8102,10 +8105,10 @@
         <v>165</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F97" s="6">
         <v>73.13</v>
@@ -8128,10 +8131,10 @@
         <v>165</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F98" s="5">
         <v>68.87</v>
@@ -8154,10 +8157,10 @@
         <v>165</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F99" s="6">
         <v>71</v>
@@ -8180,10 +8183,10 @@
         <v>165</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F100" s="5">
         <v>73.13</v>
@@ -8206,10 +8209,10 @@
         <v>165</v>
       </c>
       <c r="D101" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F101" s="6">
         <v>68.87</v>
@@ -8232,10 +8235,10 @@
         <v>165</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F102" s="5">
         <v>3.88</v>
@@ -8258,10 +8261,10 @@
         <v>165</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F103" s="6">
         <v>4</v>
@@ -8284,10 +8287,10 @@
         <v>165</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F104" s="5">
         <v>4.12</v>
@@ -8310,10 +8313,10 @@
         <v>165</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F105" s="6">
         <v>3.88</v>
@@ -8336,10 +8339,10 @@
         <v>165</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F106" s="5">
         <v>4</v>
@@ -8362,10 +8365,10 @@
         <v>165</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F107" s="6">
         <v>4.12</v>
@@ -8388,10 +8391,10 @@
         <v>165</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F108" s="5">
         <v>3.88</v>
@@ -8414,10 +8417,10 @@
         <v>165</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F109" s="6">
         <v>4.8499999999999996</v>
@@ -8440,10 +8443,10 @@
         <v>165</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F110" s="5">
         <v>5</v>
@@ -8466,10 +8469,10 @@
         <v>165</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F111" s="6">
         <v>5.15</v>
@@ -8492,10 +8495,10 @@
         <v>165</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F112" s="5">
         <v>4.8499999999999996</v>
@@ -8518,10 +8521,10 @@
         <v>165</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F113" s="6">
         <v>5</v>
@@ -8544,10 +8547,10 @@
         <v>165</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F114" s="5">
         <v>5.15</v>
@@ -8570,10 +8573,10 @@
         <v>165</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F115" s="6">
         <v>4.8499999999999996</v>
@@ -8596,10 +8599,10 @@
         <v>165</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F116" s="5">
         <v>2.91</v>
@@ -8622,10 +8625,10 @@
         <v>165</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F117" s="6">
         <v>3</v>
@@ -8648,10 +8651,10 @@
         <v>165</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F118" s="5">
         <v>3.09</v>
@@ -8674,10 +8677,10 @@
         <v>165</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F119" s="6">
         <v>2.91</v>
@@ -8700,10 +8703,10 @@
         <v>165</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F120" s="5">
         <v>3</v>
@@ -8726,10 +8729,10 @@
         <v>165</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F121" s="6">
         <v>3.09</v>
@@ -8752,10 +8755,10 @@
         <v>165</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F122" s="5">
         <v>2.91</v>
@@ -8778,10 +8781,10 @@
         <v>165</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F123" s="6">
         <v>1.94</v>
@@ -8804,10 +8807,10 @@
         <v>165</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F124" s="5">
         <v>2</v>
@@ -8830,10 +8833,10 @@
         <v>165</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F125" s="6">
         <v>2.06</v>
@@ -8856,10 +8859,10 @@
         <v>165</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F126" s="5">
         <v>1.94</v>
@@ -8882,10 +8885,10 @@
         <v>165</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F127" s="6">
         <v>2</v>
@@ -8908,10 +8911,10 @@
         <v>165</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F128" s="5">
         <v>2.06</v>
@@ -8934,10 +8937,10 @@
         <v>165</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F129" s="6">
         <v>1.94</v>
@@ -8957,13 +8960,13 @@
         <v>157</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F130" s="5">
         <v>5.6260000000000003</v>
@@ -8983,13 +8986,13 @@
         <v>157</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F131" s="6">
         <v>5.8</v>
@@ -9009,13 +9012,13 @@
         <v>157</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F132" s="5">
         <v>5.9740000000000002</v>
@@ -9035,13 +9038,13 @@
         <v>157</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F133" s="6">
         <v>5.6260000000000003</v>
@@ -9061,13 +9064,13 @@
         <v>157</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F134" s="5">
         <v>5.8</v>
@@ -9087,13 +9090,13 @@
         <v>157</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F135" s="6">
         <v>5.9740000000000002</v>
@@ -9113,13 +9116,13 @@
         <v>157</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F136" s="5">
         <v>5.6260000000000003</v>
@@ -9139,13 +9142,13 @@
         <v>157</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F137" s="6">
         <v>70.81</v>
@@ -9165,13 +9168,13 @@
         <v>157</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F138" s="5">
         <v>73</v>
@@ -9191,13 +9194,13 @@
         <v>157</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F139" s="6">
         <v>75.19</v>
@@ -9217,13 +9220,13 @@
         <v>157</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F140" s="5">
         <v>70.81</v>
@@ -9243,13 +9246,13 @@
         <v>157</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F141" s="6">
         <v>73</v>
@@ -9269,13 +9272,13 @@
         <v>157</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F142" s="5">
         <v>75.19</v>
@@ -9295,13 +9298,13 @@
         <v>157</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D143" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E143" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F143" s="6">
         <v>70.81</v>
@@ -9321,13 +9324,13 @@
         <v>157</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F144" s="5">
         <v>3.88</v>
@@ -9347,13 +9350,13 @@
         <v>157</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F145" s="6">
         <v>4</v>
@@ -9373,13 +9376,13 @@
         <v>157</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F146" s="5">
         <v>4.12</v>
@@ -9399,13 +9402,13 @@
         <v>157</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F147" s="6">
         <v>3.88</v>
@@ -9425,13 +9428,13 @@
         <v>157</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F148" s="5">
         <v>4</v>
@@ -9451,13 +9454,13 @@
         <v>157</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F149" s="6">
         <v>4.12</v>
@@ -9477,13 +9480,13 @@
         <v>157</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F150" s="5">
         <v>3.88</v>
@@ -9503,13 +9506,13 @@
         <v>157</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F151" s="6">
         <v>4.8499999999999996</v>
@@ -9529,13 +9532,13 @@
         <v>157</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F152" s="5">
         <v>5</v>
@@ -9555,13 +9558,13 @@
         <v>157</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F153" s="6">
         <v>5.15</v>
@@ -9581,13 +9584,13 @@
         <v>157</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F154" s="5">
         <v>4.8499999999999996</v>
@@ -9607,13 +9610,13 @@
         <v>157</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F155" s="6">
         <v>5</v>
@@ -9633,13 +9636,13 @@
         <v>157</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F156" s="5">
         <v>5.15</v>
@@ -9659,13 +9662,13 @@
         <v>157</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F157" s="6">
         <v>4.8499999999999996</v>
@@ -9685,13 +9688,13 @@
         <v>157</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F158" s="5">
         <v>2.91</v>
@@ -9711,13 +9714,13 @@
         <v>157</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F159" s="6">
         <v>3</v>
@@ -9737,13 +9740,13 @@
         <v>157</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F160" s="5">
         <v>3.09</v>
@@ -9763,13 +9766,13 @@
         <v>157</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F161" s="6">
         <v>2.91</v>
@@ -9789,13 +9792,13 @@
         <v>157</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F162" s="5">
         <v>3</v>
@@ -9815,13 +9818,13 @@
         <v>157</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F163" s="6">
         <v>3.09</v>
@@ -9841,13 +9844,13 @@
         <v>157</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F164" s="5">
         <v>2.91</v>
@@ -9867,13 +9870,13 @@
         <v>157</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F165" s="6">
         <v>1.94</v>
@@ -9893,13 +9896,13 @@
         <v>157</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F166" s="5">
         <v>2</v>
@@ -9919,13 +9922,13 @@
         <v>157</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F167" s="6">
         <v>2.06</v>
@@ -9945,13 +9948,13 @@
         <v>157</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F168" s="5">
         <v>1.94</v>
@@ -9971,13 +9974,13 @@
         <v>157</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F169" s="6">
         <v>2</v>
@@ -9997,13 +10000,13 @@
         <v>157</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F170" s="5">
         <v>2.06</v>
@@ -10023,13 +10026,13 @@
         <v>157</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F171" s="6">
         <v>1.94</v>
@@ -10052,10 +10055,10 @@
         <v>158</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F172" s="5">
         <v>83.42</v>
@@ -10078,10 +10081,10 @@
         <v>158</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F173" s="6">
         <v>86</v>
@@ -10104,10 +10107,10 @@
         <v>158</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F174" s="5">
         <v>88.58</v>
@@ -10130,10 +10133,10 @@
         <v>158</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F175" s="6">
         <v>83.42</v>
@@ -10156,10 +10159,10 @@
         <v>158</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F176" s="5">
         <v>86</v>
@@ -10182,10 +10185,10 @@
         <v>158</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F177" s="6">
         <v>88.58</v>
@@ -10208,10 +10211,10 @@
         <v>158</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F178" s="5">
         <v>83.42</v>
@@ -10234,10 +10237,10 @@
         <v>158</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F179" s="6">
         <v>39.770000000000003</v>
@@ -10260,10 +10263,10 @@
         <v>158</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F180" s="5">
         <v>41</v>
@@ -10286,10 +10289,10 @@
         <v>158</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F181" s="6">
         <v>42.23</v>
@@ -10312,10 +10315,10 @@
         <v>158</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F182" s="5">
         <v>39.770000000000003</v>
@@ -10338,10 +10341,10 @@
         <v>158</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F183" s="6">
         <v>41</v>
@@ -10364,10 +10367,10 @@
         <v>158</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F184" s="5">
         <v>42.23</v>
@@ -10390,10 +10393,10 @@
         <v>158</v>
       </c>
       <c r="D185" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F185" s="6">
         <v>39.770000000000003</v>
@@ -10416,10 +10419,10 @@
         <v>158</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F186" s="5">
         <v>21.34</v>
@@ -10442,10 +10445,10 @@
         <v>158</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F187" s="6">
         <v>22</v>
@@ -10468,10 +10471,10 @@
         <v>158</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F188" s="5">
         <v>22.66</v>
@@ -10494,10 +10497,10 @@
         <v>158</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F189" s="6">
         <v>21.34</v>
@@ -10520,10 +10523,10 @@
         <v>158</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F190" s="5">
         <v>22</v>
@@ -10546,10 +10549,10 @@
         <v>158</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F191" s="6">
         <v>22.66</v>
@@ -10572,10 +10575,10 @@
         <v>158</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F192" s="5">
         <v>21.34</v>
@@ -10598,10 +10601,10 @@
         <v>158</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F193" s="6">
         <v>29.1</v>
@@ -10624,10 +10627,10 @@
         <v>158</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F194" s="5">
         <v>30</v>
@@ -10650,10 +10653,10 @@
         <v>158</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F195" s="6">
         <v>30.9</v>
@@ -10676,10 +10679,10 @@
         <v>158</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F196" s="5">
         <v>29.1</v>
@@ -10702,10 +10705,10 @@
         <v>158</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F197" s="6">
         <v>30</v>
@@ -10728,10 +10731,10 @@
         <v>158</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F198" s="5">
         <v>30.9</v>
@@ -10754,10 +10757,10 @@
         <v>158</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F199" s="6">
         <v>29.1</v>
@@ -10780,10 +10783,10 @@
         <v>158</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F200" s="5">
         <v>10.67</v>
@@ -10806,10 +10809,10 @@
         <v>158</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F201" s="6">
         <v>11</v>
@@ -10832,10 +10835,10 @@
         <v>158</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F202" s="5">
         <v>11.33</v>
@@ -10858,10 +10861,10 @@
         <v>158</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F203" s="6">
         <v>10.67</v>
@@ -10884,10 +10887,10 @@
         <v>158</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F204" s="5">
         <v>11</v>
@@ -10910,10 +10913,10 @@
         <v>158</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F205" s="6">
         <v>11.33</v>
@@ -10936,10 +10939,10 @@
         <v>158</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F206" s="5">
         <v>10.67</v>
@@ -10962,10 +10965,10 @@
         <v>158</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F207" s="6">
         <v>8.73</v>
@@ -10988,10 +10991,10 @@
         <v>158</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F208" s="5">
         <v>9</v>
@@ -11014,10 +11017,10 @@
         <v>158</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F209" s="6">
         <v>9.27</v>
@@ -11040,10 +11043,10 @@
         <v>158</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E210" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F210" s="5">
         <v>8.73</v>
@@ -11066,10 +11069,10 @@
         <v>158</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F211" s="6">
         <v>9</v>
@@ -11092,10 +11095,10 @@
         <v>158</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E212" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F212" s="5">
         <v>9.27</v>
@@ -11118,10 +11121,10 @@
         <v>158</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F213" s="6">
         <v>8.73</v>
@@ -11144,10 +11147,10 @@
         <v>159</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F214" s="5">
         <v>13.773999999999999</v>
@@ -11170,10 +11173,10 @@
         <v>159</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F215" s="6">
         <v>14.2</v>
@@ -11196,10 +11199,10 @@
         <v>159</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E216" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F216" s="5">
         <v>14.625999999999999</v>
@@ -11222,10 +11225,10 @@
         <v>159</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F217" s="6">
         <v>13.773999999999999</v>
@@ -11248,10 +11251,10 @@
         <v>159</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F218" s="5">
         <v>14.2</v>
@@ -11274,10 +11277,10 @@
         <v>159</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F219" s="6">
         <v>14.625999999999999</v>
@@ -11300,10 +11303,10 @@
         <v>159</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E220" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F220" s="5">
         <v>13.773999999999999</v>
@@ -11326,10 +11329,10 @@
         <v>159</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F221" s="6">
         <v>82.45</v>
@@ -11352,10 +11355,10 @@
         <v>159</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E222" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F222" s="5">
         <v>85</v>
@@ -11378,10 +11381,10 @@
         <v>159</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F223" s="6">
         <v>87.55</v>
@@ -11404,10 +11407,10 @@
         <v>159</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E224" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F224" s="5">
         <v>82.45</v>
@@ -11430,10 +11433,10 @@
         <v>159</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F225" s="6">
         <v>85</v>
@@ -11456,10 +11459,10 @@
         <v>159</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E226" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F226" s="5">
         <v>87.55</v>
@@ -11482,10 +11485,10 @@
         <v>159</v>
       </c>
       <c r="D227" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E227" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F227" s="6">
         <v>82.45</v>
@@ -11508,10 +11511,10 @@
         <v>159</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F228" s="5">
         <v>8.73</v>
@@ -11534,10 +11537,10 @@
         <v>159</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F229" s="6">
         <v>9</v>
@@ -11560,10 +11563,10 @@
         <v>159</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E230" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F230" s="5">
         <v>9.27</v>
@@ -11586,10 +11589,10 @@
         <v>159</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F231" s="6">
         <v>8.73</v>
@@ -11612,10 +11615,10 @@
         <v>159</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F232" s="5">
         <v>9</v>
@@ -11638,10 +11641,10 @@
         <v>159</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F233" s="6">
         <v>9.27</v>
@@ -11664,10 +11667,10 @@
         <v>159</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F234" s="5">
         <v>8.73</v>
@@ -11690,10 +11693,10 @@
         <v>159</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F235" s="6">
         <v>11.64</v>
@@ -11716,10 +11719,10 @@
         <v>159</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F236" s="5">
         <v>12</v>
@@ -11742,10 +11745,10 @@
         <v>159</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F237" s="6">
         <v>12.36</v>
@@ -11768,10 +11771,10 @@
         <v>159</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F238" s="5">
         <v>11.64</v>
@@ -11794,10 +11797,10 @@
         <v>159</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F239" s="6">
         <v>12</v>
@@ -11820,10 +11823,10 @@
         <v>159</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E240" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F240" s="5">
         <v>12.36</v>
@@ -11846,10 +11849,10 @@
         <v>159</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F241" s="6">
         <v>11.64</v>
@@ -11872,10 +11875,10 @@
         <v>159</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E242" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F242" s="5">
         <v>5.82</v>
@@ -11898,10 +11901,10 @@
         <v>159</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F243" s="6">
         <v>6</v>
@@ -11924,10 +11927,10 @@
         <v>159</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E244" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F244" s="5">
         <v>6.18</v>
@@ -11950,10 +11953,10 @@
         <v>159</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F245" s="6">
         <v>5.82</v>
@@ -11976,10 +11979,10 @@
         <v>159</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E246" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F246" s="5">
         <v>6</v>
@@ -12002,10 +12005,10 @@
         <v>159</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F247" s="6">
         <v>6.18</v>
@@ -12028,10 +12031,10 @@
         <v>159</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E248" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F248" s="5">
         <v>5.82</v>
@@ -12054,10 +12057,10 @@
         <v>159</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F249" s="6">
         <v>3.88</v>
@@ -12080,10 +12083,10 @@
         <v>159</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E250" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F250" s="5">
         <v>4</v>
@@ -12106,10 +12109,10 @@
         <v>159</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F251" s="6">
         <v>4.12</v>
@@ -12132,10 +12135,10 @@
         <v>159</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E252" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F252" s="5">
         <v>3.88</v>
@@ -12158,10 +12161,10 @@
         <v>159</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F253" s="6">
         <v>4</v>
@@ -12184,10 +12187,10 @@
         <v>159</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E254" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F254" s="5">
         <v>4.12</v>
@@ -12210,10 +12213,10 @@
         <v>159</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F255" s="6">
         <v>3.88</v>
@@ -12230,16 +12233,16 @@
         <v>67</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E256" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F256" s="5">
         <v>3.0070000000000001</v>
@@ -12256,16 +12259,16 @@
         <v>67</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F257" s="6">
         <v>3.1</v>
@@ -12282,16 +12285,16 @@
         <v>67</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E258" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F258" s="5">
         <v>3.1930000000000001</v>
@@ -12308,16 +12311,16 @@
         <v>67</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F259" s="6">
         <v>3.0070000000000001</v>
@@ -12334,16 +12337,16 @@
         <v>67</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E260" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F260" s="5">
         <v>3.1</v>
@@ -12360,16 +12363,16 @@
         <v>67</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F261" s="6">
         <v>3.1930000000000001</v>
@@ -12386,16 +12389,16 @@
         <v>67</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E262" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F262" s="5">
         <v>3.0070000000000001</v>
@@ -12412,16 +12415,16 @@
         <v>67</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F263" s="6">
         <v>85.36</v>
@@ -12438,16 +12441,16 @@
         <v>67</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E264" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F264" s="5">
         <v>88</v>
@@ -12464,16 +12467,16 @@
         <v>67</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F265" s="6">
         <v>90.64</v>
@@ -12490,16 +12493,16 @@
         <v>67</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E266" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F266" s="5">
         <v>85.36</v>
@@ -12516,16 +12519,16 @@
         <v>67</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F267" s="6">
         <v>88</v>
@@ -12542,16 +12545,16 @@
         <v>67</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E268" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F268" s="5">
         <v>90.64</v>
@@ -12568,16 +12571,16 @@
         <v>67</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D269" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E269" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F269" s="6">
         <v>85.36</v>
@@ -12594,16 +12597,16 @@
         <v>67</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E270" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F270" s="5">
         <v>1.94</v>
@@ -12620,16 +12623,16 @@
         <v>67</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F271" s="6">
         <v>2</v>
@@ -12646,16 +12649,16 @@
         <v>67</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E272" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F272" s="5">
         <v>2.06</v>
@@ -12672,16 +12675,16 @@
         <v>67</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F273" s="6">
         <v>1.94</v>
@@ -12698,16 +12701,16 @@
         <v>67</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E274" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F274" s="5">
         <v>2</v>
@@ -12724,16 +12727,16 @@
         <v>67</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F275" s="6">
         <v>2.06</v>
@@ -12750,16 +12753,16 @@
         <v>67</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E276" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F276" s="5">
         <v>1.94</v>
@@ -12776,16 +12779,16 @@
         <v>67</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F277" s="6">
         <v>1.94</v>
@@ -12802,16 +12805,16 @@
         <v>67</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E278" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F278" s="5">
         <v>2</v>
@@ -12828,16 +12831,16 @@
         <v>67</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F279" s="6">
         <v>2.06</v>
@@ -12854,16 +12857,16 @@
         <v>67</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E280" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F280" s="5">
         <v>1.94</v>
@@ -12880,16 +12883,16 @@
         <v>67</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F281" s="6">
         <v>2</v>
@@ -12906,16 +12909,16 @@
         <v>67</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E282" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F282" s="5">
         <v>2.06</v>
@@ -12932,16 +12935,16 @@
         <v>67</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F283" s="6">
         <v>1.94</v>
@@ -12958,16 +12961,16 @@
         <v>67</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E284" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F284" s="5">
         <v>0.97</v>
@@ -12984,16 +12987,16 @@
         <v>67</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F285" s="6">
         <v>1</v>
@@ -13010,16 +13013,16 @@
         <v>67</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E286" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F286" s="5">
         <v>1.03</v>
@@ -13036,16 +13039,16 @@
         <v>67</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F287" s="6">
         <v>0.97</v>
@@ -13062,16 +13065,16 @@
         <v>67</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E288" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F288" s="5">
         <v>1</v>
@@ -13088,16 +13091,16 @@
         <v>67</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F289" s="6">
         <v>1.03</v>
@@ -13114,16 +13117,16 @@
         <v>67</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E290" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F290" s="5">
         <v>0.97</v>
@@ -13140,16 +13143,16 @@
         <v>67</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F291" s="6">
         <v>0.97</v>
@@ -13166,16 +13169,16 @@
         <v>67</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E292" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F292" s="5">
         <v>1</v>
@@ -13192,16 +13195,16 @@
         <v>67</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F293" s="6">
         <v>1.03</v>
@@ -13218,16 +13221,16 @@
         <v>67</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E294" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F294" s="5">
         <v>0.97</v>
@@ -13244,16 +13247,16 @@
         <v>67</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F295" s="6">
         <v>1</v>
@@ -13270,16 +13273,16 @@
         <v>67</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E296" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F296" s="5">
         <v>1.03</v>
@@ -13296,16 +13299,16 @@
         <v>67</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F297" s="6">
         <v>0.97</v>
@@ -13328,10 +13331,10 @@
         <v>153</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E298" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F298" s="5">
         <v>23.765000000000001</v>
@@ -13354,10 +13357,10 @@
         <v>153</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F299" s="6">
         <v>24.5</v>
@@ -13380,10 +13383,10 @@
         <v>153</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E300" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F300" s="5">
         <v>25.234999999999999</v>
@@ -13406,10 +13409,10 @@
         <v>153</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F301" s="6">
         <v>23.765000000000001</v>
@@ -13432,10 +13435,10 @@
         <v>153</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E302" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F302" s="5">
         <v>24.5</v>
@@ -13458,10 +13461,10 @@
         <v>153</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F303" s="6">
         <v>25.234999999999999</v>
@@ -13484,10 +13487,10 @@
         <v>153</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E304" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F304" s="5">
         <v>23.765000000000001</v>
@@ -13510,10 +13513,10 @@
         <v>153</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F305" s="6">
         <v>56.26</v>
@@ -13536,10 +13539,10 @@
         <v>153</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E306" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F306" s="5">
         <v>58</v>
@@ -13562,10 +13565,10 @@
         <v>153</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F307" s="6">
         <v>59.74</v>
@@ -13588,10 +13591,10 @@
         <v>153</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E308" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F308" s="5">
         <v>56.26</v>
@@ -13614,10 +13617,10 @@
         <v>153</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F309" s="6">
         <v>58</v>
@@ -13640,10 +13643,10 @@
         <v>153</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E310" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F310" s="5">
         <v>59.74</v>
@@ -13666,10 +13669,10 @@
         <v>153</v>
       </c>
       <c r="D311" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E311" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E311" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F311" s="6">
         <v>56.26</v>
@@ -13692,10 +13695,10 @@
         <v>153</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E312" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F312" s="5">
         <v>5.82</v>
@@ -13718,10 +13721,10 @@
         <v>153</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F313" s="6">
         <v>6</v>
@@ -13744,10 +13747,10 @@
         <v>153</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E314" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F314" s="5">
         <v>6.18</v>
@@ -13770,10 +13773,10 @@
         <v>153</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F315" s="6">
         <v>5.82</v>
@@ -13796,10 +13799,10 @@
         <v>153</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E316" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F316" s="5">
         <v>6</v>
@@ -13822,10 +13825,10 @@
         <v>153</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F317" s="6">
         <v>6.18</v>
@@ -13848,10 +13851,10 @@
         <v>153</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E318" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F318" s="5">
         <v>5.82</v>
@@ -13874,10 +13877,10 @@
         <v>153</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F319" s="6">
         <v>7.76</v>
@@ -13900,10 +13903,10 @@
         <v>153</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E320" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F320" s="5">
         <v>8</v>
@@ -13926,10 +13929,10 @@
         <v>153</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F321" s="6">
         <v>8.24</v>
@@ -13952,10 +13955,10 @@
         <v>153</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E322" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F322" s="5">
         <v>7.76</v>
@@ -13978,10 +13981,10 @@
         <v>153</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F323" s="6">
         <v>8</v>
@@ -14004,10 +14007,10 @@
         <v>153</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E324" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F324" s="5">
         <v>8.24</v>
@@ -14030,10 +14033,10 @@
         <v>153</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F325" s="6">
         <v>7.76</v>
@@ -14056,10 +14059,10 @@
         <v>153</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E326" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F326" s="5">
         <v>3.88</v>
@@ -14082,10 +14085,10 @@
         <v>153</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F327" s="6">
         <v>4</v>
@@ -14108,10 +14111,10 @@
         <v>153</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E328" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F328" s="5">
         <v>4.12</v>
@@ -14134,10 +14137,10 @@
         <v>153</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F329" s="6">
         <v>3.88</v>
@@ -14160,10 +14163,10 @@
         <v>153</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E330" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F330" s="5">
         <v>4</v>
@@ -14186,10 +14189,10 @@
         <v>153</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F331" s="6">
         <v>4.12</v>
@@ -14212,10 +14215,10 @@
         <v>153</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E332" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F332" s="5">
         <v>3.88</v>
@@ -14238,10 +14241,10 @@
         <v>153</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F333" s="6">
         <v>2.91</v>
@@ -14264,10 +14267,10 @@
         <v>153</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E334" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F334" s="5">
         <v>3</v>
@@ -14290,10 +14293,10 @@
         <v>153</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F335" s="6">
         <v>3.09</v>
@@ -14316,10 +14319,10 @@
         <v>153</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E336" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F336" s="5">
         <v>2.91</v>
@@ -14342,10 +14345,10 @@
         <v>153</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F337" s="6">
         <v>3</v>
@@ -14368,10 +14371,10 @@
         <v>153</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E338" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F338" s="5">
         <v>3.09</v>
@@ -14394,10 +14397,10 @@
         <v>153</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F339" s="6">
         <v>2.91</v>
@@ -14420,10 +14423,10 @@
         <v>156</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E340" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F340" s="5">
         <v>23.085999999999999</v>
@@ -14446,10 +14449,10 @@
         <v>156</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F341" s="6">
         <v>23.8</v>
@@ -14472,10 +14475,10 @@
         <v>156</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E342" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F342" s="5">
         <v>24.513999999999999</v>
@@ -14498,10 +14501,10 @@
         <v>156</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F343" s="6">
         <v>23.085999999999999</v>
@@ -14524,10 +14527,10 @@
         <v>156</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E344" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F344" s="5">
         <v>23.8</v>
@@ -14550,10 +14553,10 @@
         <v>156</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F345" s="6">
         <v>24.513999999999999</v>
@@ -14576,10 +14579,10 @@
         <v>156</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E346" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F346" s="5">
         <v>23.085999999999999</v>
@@ -14602,10 +14605,10 @@
         <v>156</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F347" s="6">
         <v>55.29</v>
@@ -14628,10 +14631,10 @@
         <v>156</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E348" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F348" s="5">
         <v>57</v>
@@ -14654,10 +14657,10 @@
         <v>156</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F349" s="6">
         <v>58.71</v>
@@ -14680,10 +14683,10 @@
         <v>156</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E350" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F350" s="5">
         <v>55.29</v>
@@ -14706,10 +14709,10 @@
         <v>156</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F351" s="6">
         <v>57</v>
@@ -14732,10 +14735,10 @@
         <v>156</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E352" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F352" s="5">
         <v>58.71</v>
@@ -14758,10 +14761,10 @@
         <v>156</v>
       </c>
       <c r="D353" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E353" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E353" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F353" s="6">
         <v>55.29</v>
@@ -14784,10 +14787,10 @@
         <v>156</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E354" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F354" s="5">
         <v>5.82</v>
@@ -14810,10 +14813,10 @@
         <v>156</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F355" s="6">
         <v>6</v>
@@ -14836,10 +14839,10 @@
         <v>156</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E356" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F356" s="5">
         <v>6.18</v>
@@ -14862,10 +14865,10 @@
         <v>156</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F357" s="6">
         <v>5.82</v>
@@ -14888,10 +14891,10 @@
         <v>156</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E358" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F358" s="5">
         <v>6</v>
@@ -14914,10 +14917,10 @@
         <v>156</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F359" s="6">
         <v>6.18</v>
@@ -14940,10 +14943,10 @@
         <v>156</v>
       </c>
       <c r="D360" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E360" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F360" s="5">
         <v>5.82</v>
@@ -14966,10 +14969,10 @@
         <v>156</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F361" s="6">
         <v>7.76</v>
@@ -14992,10 +14995,10 @@
         <v>156</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E362" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F362" s="5">
         <v>8</v>
@@ -15018,10 +15021,10 @@
         <v>156</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F363" s="6">
         <v>8.24</v>
@@ -15044,10 +15047,10 @@
         <v>156</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E364" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F364" s="5">
         <v>7.76</v>
@@ -15070,10 +15073,10 @@
         <v>156</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F365" s="6">
         <v>8</v>
@@ -15096,10 +15099,10 @@
         <v>156</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E366" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F366" s="5">
         <v>8.24</v>
@@ -15122,10 +15125,10 @@
         <v>156</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F367" s="6">
         <v>7.76</v>
@@ -15148,10 +15151,10 @@
         <v>156</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E368" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F368" s="5">
         <v>3.88</v>
@@ -15174,10 +15177,10 @@
         <v>156</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F369" s="6">
         <v>4</v>
@@ -15200,10 +15203,10 @@
         <v>156</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E370" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F370" s="5">
         <v>4.12</v>
@@ -15226,10 +15229,10 @@
         <v>156</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F371" s="6">
         <v>3.88</v>
@@ -15252,10 +15255,10 @@
         <v>156</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E372" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F372" s="5">
         <v>4</v>
@@ -15278,10 +15281,10 @@
         <v>156</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F373" s="6">
         <v>4.12</v>
@@ -15304,10 +15307,10 @@
         <v>156</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E374" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F374" s="5">
         <v>3.88</v>
@@ -15330,10 +15333,10 @@
         <v>156</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F375" s="6">
         <v>2.91</v>
@@ -15356,10 +15359,10 @@
         <v>156</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E376" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F376" s="5">
         <v>3</v>
@@ -15382,10 +15385,10 @@
         <v>156</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F377" s="6">
         <v>3.09</v>
@@ -15408,10 +15411,10 @@
         <v>156</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E378" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F378" s="5">
         <v>2.91</v>
@@ -15434,10 +15437,10 @@
         <v>156</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F379" s="6">
         <v>3</v>
@@ -15460,10 +15463,10 @@
         <v>156</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E380" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F380" s="5">
         <v>3.09</v>
@@ -15486,10 +15489,10 @@
         <v>156</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F381" s="6">
         <v>2.91</v>
@@ -15512,10 +15515,10 @@
         <v>141</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E382" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F382" s="5">
         <v>12.028</v>
@@ -15538,10 +15541,10 @@
         <v>141</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F383" s="6">
         <v>12.4</v>
@@ -15564,10 +15567,10 @@
         <v>141</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E384" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F384" s="5">
         <v>12.772</v>
@@ -15590,10 +15593,10 @@
         <v>141</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F385" s="6">
         <v>12.028</v>
@@ -15616,10 +15619,10 @@
         <v>141</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E386" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F386" s="5">
         <v>12.4</v>
@@ -15642,10 +15645,10 @@
         <v>141</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F387" s="6">
         <v>12.772</v>
@@ -15668,10 +15671,10 @@
         <v>141</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E388" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F388" s="5">
         <v>12.028</v>
@@ -15694,10 +15697,10 @@
         <v>141</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F389" s="6">
         <v>81.48</v>
@@ -15720,10 +15723,10 @@
         <v>141</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E390" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F390" s="5">
         <v>84</v>
@@ -15746,10 +15749,10 @@
         <v>141</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F391" s="6">
         <v>86.52</v>
@@ -15772,10 +15775,10 @@
         <v>141</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E392" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F392" s="5">
         <v>81.48</v>
@@ -15798,10 +15801,10 @@
         <v>141</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F393" s="6">
         <v>84</v>
@@ -15824,10 +15827,10 @@
         <v>141</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E394" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F394" s="5">
         <v>86.52</v>
@@ -15850,10 +15853,10 @@
         <v>141</v>
       </c>
       <c r="D395" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E395" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E395" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F395" s="6">
         <v>81.48</v>
@@ -15876,10 +15879,10 @@
         <v>141</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E396" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F396" s="5">
         <v>13.58</v>
@@ -15902,10 +15905,10 @@
         <v>141</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F397" s="6">
         <v>14</v>
@@ -15928,10 +15931,10 @@
         <v>141</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E398" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F398" s="5">
         <v>14.42</v>
@@ -15954,10 +15957,10 @@
         <v>141</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F399" s="6">
         <v>13.58</v>
@@ -15980,10 +15983,10 @@
         <v>141</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E400" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F400" s="5">
         <v>14</v>
@@ -16006,10 +16009,10 @@
         <v>141</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F401" s="6">
         <v>14.42</v>
@@ -16032,10 +16035,10 @@
         <v>141</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E402" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F402" s="5">
         <v>13.58</v>
@@ -16058,10 +16061,10 @@
         <v>141</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F403" s="6">
         <v>20.37</v>
@@ -16084,10 +16087,10 @@
         <v>141</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E404" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F404" s="5">
         <v>21</v>
@@ -16110,10 +16113,10 @@
         <v>141</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F405" s="6">
         <v>21.63</v>
@@ -16136,10 +16139,10 @@
         <v>141</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E406" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F406" s="5">
         <v>20.37</v>
@@ -16162,10 +16165,10 @@
         <v>141</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F407" s="6">
         <v>21</v>
@@ -16188,10 +16191,10 @@
         <v>141</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E408" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F408" s="5">
         <v>21.63</v>
@@ -16214,10 +16217,10 @@
         <v>141</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F409" s="6">
         <v>20.37</v>
@@ -16240,10 +16243,10 @@
         <v>141</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E410" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F410" s="5">
         <v>6.79</v>
@@ -16266,10 +16269,10 @@
         <v>141</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F411" s="6">
         <v>7</v>
@@ -16292,10 +16295,10 @@
         <v>141</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E412" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F412" s="5">
         <v>7.21</v>
@@ -16318,10 +16321,10 @@
         <v>141</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F413" s="6">
         <v>6.79</v>
@@ -16344,10 +16347,10 @@
         <v>141</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E414" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F414" s="5">
         <v>7</v>
@@ -16370,10 +16373,10 @@
         <v>141</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F415" s="6">
         <v>7.21</v>
@@ -16396,10 +16399,10 @@
         <v>141</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E416" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F416" s="5">
         <v>6.79</v>
@@ -16422,10 +16425,10 @@
         <v>141</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F417" s="6">
         <v>4.8499999999999996</v>
@@ -16448,10 +16451,10 @@
         <v>141</v>
       </c>
       <c r="D418" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E418" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F418" s="5">
         <v>5</v>
@@ -16474,10 +16477,10 @@
         <v>141</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F419" s="6">
         <v>5.15</v>
@@ -16500,10 +16503,10 @@
         <v>141</v>
       </c>
       <c r="D420" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E420" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F420" s="5">
         <v>4.8499999999999996</v>
@@ -16526,10 +16529,10 @@
         <v>141</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F421" s="6">
         <v>5</v>
@@ -16552,10 +16555,10 @@
         <v>141</v>
       </c>
       <c r="D422" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E422" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F422" s="5">
         <v>5.15</v>
@@ -16578,10 +16581,10 @@
         <v>141</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F423" s="6">
         <v>4.8499999999999996</v>
@@ -16604,10 +16607,10 @@
         <v>147</v>
       </c>
       <c r="D424" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E424" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F424" s="5">
         <v>30.07</v>
@@ -16630,10 +16633,10 @@
         <v>147</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F425" s="6">
         <v>31</v>
@@ -16656,10 +16659,10 @@
         <v>147</v>
       </c>
       <c r="D426" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E426" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F426" s="5">
         <v>31.93</v>
@@ -16682,10 +16685,10 @@
         <v>147</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F427" s="6">
         <v>30.07</v>
@@ -16708,10 +16711,10 @@
         <v>147</v>
       </c>
       <c r="D428" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E428" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F428" s="5">
         <v>31</v>
@@ -16734,10 +16737,10 @@
         <v>147</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F429" s="6">
         <v>31.93</v>
@@ -16760,10 +16763,10 @@
         <v>147</v>
       </c>
       <c r="D430" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E430" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F430" s="5">
         <v>30.07</v>
@@ -16786,10 +16789,10 @@
         <v>147</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F431" s="6">
         <v>60.14</v>
@@ -16812,10 +16815,10 @@
         <v>147</v>
       </c>
       <c r="D432" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E432" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F432" s="5">
         <v>62</v>
@@ -16838,10 +16841,10 @@
         <v>147</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F433" s="6">
         <v>63.86</v>
@@ -16864,10 +16867,10 @@
         <v>147</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E434" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F434" s="5">
         <v>60.14</v>
@@ -16890,10 +16893,10 @@
         <v>147</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F435" s="6">
         <v>62</v>
@@ -16916,10 +16919,10 @@
         <v>147</v>
       </c>
       <c r="D436" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E436" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F436" s="5">
         <v>63.86</v>
@@ -16942,10 +16945,10 @@
         <v>147</v>
       </c>
       <c r="D437" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E437" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E437" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F437" s="6">
         <v>60.14</v>
@@ -16968,10 +16971,10 @@
         <v>147</v>
       </c>
       <c r="D438" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E438" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F438" s="5">
         <v>10.67</v>
@@ -16994,10 +16997,10 @@
         <v>147</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F439" s="6">
         <v>11</v>
@@ -17020,10 +17023,10 @@
         <v>147</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E440" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F440" s="5">
         <v>11.33</v>
@@ -17046,10 +17049,10 @@
         <v>147</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F441" s="6">
         <v>10.67</v>
@@ -17072,10 +17075,10 @@
         <v>147</v>
       </c>
       <c r="D442" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E442" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F442" s="5">
         <v>11</v>
@@ -17098,10 +17101,10 @@
         <v>147</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F443" s="6">
         <v>11.33</v>
@@ -17124,10 +17127,10 @@
         <v>147</v>
       </c>
       <c r="D444" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E444" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F444" s="5">
         <v>10.67</v>
@@ -17150,10 +17153,10 @@
         <v>147</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F445" s="6">
         <v>15.52</v>
@@ -17176,10 +17179,10 @@
         <v>147</v>
       </c>
       <c r="D446" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E446" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F446" s="5">
         <v>16</v>
@@ -17202,10 +17205,10 @@
         <v>147</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F447" s="6">
         <v>16.48</v>
@@ -17228,10 +17231,10 @@
         <v>147</v>
       </c>
       <c r="D448" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E448" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F448" s="5">
         <v>15.52</v>
@@ -17254,10 +17257,10 @@
         <v>147</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F449" s="6">
         <v>16</v>
@@ -17280,10 +17283,10 @@
         <v>147</v>
       </c>
       <c r="D450" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E450" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F450" s="5">
         <v>16.48</v>
@@ -17306,10 +17309,10 @@
         <v>147</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F451" s="6">
         <v>15.52</v>
@@ -17332,10 +17335,10 @@
         <v>147</v>
       </c>
       <c r="D452" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E452" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F452" s="5">
         <v>6.79</v>
@@ -17358,10 +17361,10 @@
         <v>147</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F453" s="6">
         <v>7</v>
@@ -17384,10 +17387,10 @@
         <v>147</v>
       </c>
       <c r="D454" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E454" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F454" s="5">
         <v>7.21</v>
@@ -17410,10 +17413,10 @@
         <v>147</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F455" s="6">
         <v>6.79</v>
@@ -17436,10 +17439,10 @@
         <v>147</v>
       </c>
       <c r="D456" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E456" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F456" s="5">
         <v>7</v>
@@ -17462,10 +17465,10 @@
         <v>147</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F457" s="6">
         <v>7.21</v>
@@ -17488,10 +17491,10 @@
         <v>147</v>
       </c>
       <c r="D458" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E458" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F458" s="5">
         <v>6.79</v>
@@ -17514,10 +17517,10 @@
         <v>147</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F459" s="6">
         <v>4.8499999999999996</v>
@@ -17540,10 +17543,10 @@
         <v>147</v>
       </c>
       <c r="D460" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E460" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F460" s="5">
         <v>5</v>
@@ -17566,10 +17569,10 @@
         <v>147</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F461" s="6">
         <v>5.15</v>
@@ -17592,10 +17595,10 @@
         <v>147</v>
       </c>
       <c r="D462" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E462" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F462" s="5">
         <v>4.8499999999999996</v>
@@ -17618,10 +17621,10 @@
         <v>147</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F463" s="6">
         <v>5</v>
@@ -17644,10 +17647,10 @@
         <v>147</v>
       </c>
       <c r="D464" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E464" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F464" s="5">
         <v>5.15</v>
@@ -17670,10 +17673,10 @@
         <v>147</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F465" s="6">
         <v>4.8499999999999996</v>
@@ -17710,7 +17713,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B1" s="14"/>
     </row>
@@ -17730,106 +17733,106 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-kk_29knp\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-lhcbnfs4\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C32AF4-610C-4D11-A36D-8C627F83C726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4B471E-03C1-4DDA-A081-9119C4AC1A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3645" yWindow="-13320" windowWidth="5970" windowHeight="10455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -1054,7 +1054,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C71D-454C-A174-2F475DD86964}"/>
+              <c16:uniqueId val="{00000000-3A00-49D4-B462-4097E1D88DBA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1154,7 +1154,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C71D-454C-A174-2F475DD86964}"/>
+              <c16:uniqueId val="{00000001-3A00-49D4-B462-4097E1D88DBA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1278,7 +1278,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-A592-4410-8E57-7E0DDEF470C3}"/>
+                <c16:uniqueId val="{00000001-31D4-45A1-8176-E05B414E138B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1288,7 +1288,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-A592-4410-8E57-7E0DDEF470C3}"/>
+                <c16:uniqueId val="{00000003-31D4-45A1-8176-E05B414E138B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1298,7 +1298,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-A592-4410-8E57-7E0DDEF470C3}"/>
+                <c16:uniqueId val="{00000005-31D4-45A1-8176-E05B414E138B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1354,7 +1354,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-A592-4410-8E57-7E0DDEF470C3}"/>
+              <c16:uniqueId val="{00000006-31D4-45A1-8176-E05B414E138B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1509,7 +1509,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FD32-43C4-B2C6-9453C50DB88A}"/>
+              <c16:uniqueId val="{00000000-6260-4742-BFB0-3211CE5E9C70}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1629,7 +1629,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
+                <c16:uniqueId val="{00000001-F02D-4BE8-B157-9DC6F7C95986}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1639,7 +1639,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
+                <c16:uniqueId val="{00000003-F02D-4BE8-B157-9DC6F7C95986}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1649,7 +1649,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
+                <c16:uniqueId val="{00000005-F02D-4BE8-B157-9DC6F7C95986}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1659,7 +1659,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
+                <c16:uniqueId val="{00000007-F02D-4BE8-B157-9DC6F7C95986}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1669,7 +1669,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
+                <c16:uniqueId val="{00000009-F02D-4BE8-B157-9DC6F7C95986}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1679,7 +1679,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
+                <c16:uniqueId val="{0000000B-F02D-4BE8-B157-9DC6F7C95986}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1753,7 +1753,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-5FFF-432D-A5AB-5FA6EDC31BF0}"/>
+              <c16:uniqueId val="{0000000C-F02D-4BE8-B157-9DC6F7C95986}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-lhcbnfs4\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-yb_0tvu1\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4B471E-03C1-4DDA-A081-9119C4AC1A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9512637C-3CC8-4670-8E15-D4C05833E573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1054,7 +1054,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3A00-49D4-B462-4097E1D88DBA}"/>
+              <c16:uniqueId val="{00000000-2146-473C-A6A1-DFF27DE01AFA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1154,7 +1154,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3A00-49D4-B462-4097E1D88DBA}"/>
+              <c16:uniqueId val="{00000001-2146-473C-A6A1-DFF27DE01AFA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1278,7 +1278,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-31D4-45A1-8176-E05B414E138B}"/>
+                <c16:uniqueId val="{00000001-DA24-42D0-B44E-BFC58FBC9074}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1288,7 +1288,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-31D4-45A1-8176-E05B414E138B}"/>
+                <c16:uniqueId val="{00000003-DA24-42D0-B44E-BFC58FBC9074}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1298,7 +1298,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-31D4-45A1-8176-E05B414E138B}"/>
+                <c16:uniqueId val="{00000005-DA24-42D0-B44E-BFC58FBC9074}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1354,7 +1354,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-31D4-45A1-8176-E05B414E138B}"/>
+              <c16:uniqueId val="{00000006-DA24-42D0-B44E-BFC58FBC9074}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1509,7 +1509,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6260-4742-BFB0-3211CE5E9C70}"/>
+              <c16:uniqueId val="{00000000-F9EC-4533-ABCB-A925435E446B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1629,7 +1629,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F02D-4BE8-B157-9DC6F7C95986}"/>
+                <c16:uniqueId val="{00000001-8793-40B4-BF9E-4075BC9259FE}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1639,7 +1639,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F02D-4BE8-B157-9DC6F7C95986}"/>
+                <c16:uniqueId val="{00000003-8793-40B4-BF9E-4075BC9259FE}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1649,7 +1649,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F02D-4BE8-B157-9DC6F7C95986}"/>
+                <c16:uniqueId val="{00000005-8793-40B4-BF9E-4075BC9259FE}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1659,7 +1659,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-F02D-4BE8-B157-9DC6F7C95986}"/>
+                <c16:uniqueId val="{00000007-8793-40B4-BF9E-4075BC9259FE}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1669,7 +1669,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-F02D-4BE8-B157-9DC6F7C95986}"/>
+                <c16:uniqueId val="{00000009-8793-40B4-BF9E-4075BC9259FE}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1679,7 +1679,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-F02D-4BE8-B157-9DC6F7C95986}"/>
+                <c16:uniqueId val="{0000000B-8793-40B4-BF9E-4075BC9259FE}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1753,7 +1753,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-F02D-4BE8-B157-9DC6F7C95986}"/>
+              <c16:uniqueId val="{0000000C-8793-40B4-BF9E-4075BC9259FE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-yb_0tvu1\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-09jfy2fk\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9512637C-3CC8-4670-8E15-D4C05833E573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66285B8-2C2E-47E4-B1FC-9316E3C228FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -1054,7 +1054,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2146-473C-A6A1-DFF27DE01AFA}"/>
+              <c16:uniqueId val="{00000000-5143-4D44-BDBD-7F5ECB3ACBC6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1154,7 +1154,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2146-473C-A6A1-DFF27DE01AFA}"/>
+              <c16:uniqueId val="{00000001-5143-4D44-BDBD-7F5ECB3ACBC6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1278,7 +1278,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-DA24-42D0-B44E-BFC58FBC9074}"/>
+                <c16:uniqueId val="{00000001-BF22-4DF2-B28C-3528E774FCF3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1288,7 +1288,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-DA24-42D0-B44E-BFC58FBC9074}"/>
+                <c16:uniqueId val="{00000003-BF22-4DF2-B28C-3528E774FCF3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1298,7 +1298,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-DA24-42D0-B44E-BFC58FBC9074}"/>
+                <c16:uniqueId val="{00000005-BF22-4DF2-B28C-3528E774FCF3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1354,7 +1354,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-DA24-42D0-B44E-BFC58FBC9074}"/>
+              <c16:uniqueId val="{00000006-BF22-4DF2-B28C-3528E774FCF3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1509,7 +1509,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F9EC-4533-ABCB-A925435E446B}"/>
+              <c16:uniqueId val="{00000000-1883-4677-869D-66D9E0F8764E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1629,7 +1629,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-8793-40B4-BF9E-4075BC9259FE}"/>
+                <c16:uniqueId val="{00000001-FF76-4F65-B10D-2059C4C0A570}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1639,7 +1639,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-8793-40B4-BF9E-4075BC9259FE}"/>
+                <c16:uniqueId val="{00000003-FF76-4F65-B10D-2059C4C0A570}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1649,7 +1649,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-8793-40B4-BF9E-4075BC9259FE}"/>
+                <c16:uniqueId val="{00000005-FF76-4F65-B10D-2059C4C0A570}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1659,7 +1659,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-8793-40B4-BF9E-4075BC9259FE}"/>
+                <c16:uniqueId val="{00000007-FF76-4F65-B10D-2059C4C0A570}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1669,7 +1669,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-8793-40B4-BF9E-4075BC9259FE}"/>
+                <c16:uniqueId val="{00000009-FF76-4F65-B10D-2059C4C0A570}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1679,7 +1679,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-8793-40B4-BF9E-4075BC9259FE}"/>
+                <c16:uniqueId val="{0000000B-FF76-4F65-B10D-2059C4C0A570}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1753,7 +1753,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-8793-40B4-BF9E-4075BC9259FE}"/>
+              <c16:uniqueId val="{0000000C-FF76-4F65-B10D-2059C4C0A570}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-09jfy2fk\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-5yxkm8zf\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66285B8-2C2E-47E4-B1FC-9316E3C228FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9722442A-3029-4AA0-A9CC-E13006E31BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -1054,7 +1054,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5143-4D44-BDBD-7F5ECB3ACBC6}"/>
+              <c16:uniqueId val="{00000000-16C4-4621-B345-9C2E5DBE8B8B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1154,7 +1154,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5143-4D44-BDBD-7F5ECB3ACBC6}"/>
+              <c16:uniqueId val="{00000001-16C4-4621-B345-9C2E5DBE8B8B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1278,7 +1278,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-BF22-4DF2-B28C-3528E774FCF3}"/>
+                <c16:uniqueId val="{00000001-D09D-4669-AAE7-BA22EB458689}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1288,7 +1288,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-BF22-4DF2-B28C-3528E774FCF3}"/>
+                <c16:uniqueId val="{00000003-D09D-4669-AAE7-BA22EB458689}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1298,7 +1298,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-BF22-4DF2-B28C-3528E774FCF3}"/>
+                <c16:uniqueId val="{00000005-D09D-4669-AAE7-BA22EB458689}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1354,7 +1354,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-BF22-4DF2-B28C-3528E774FCF3}"/>
+              <c16:uniqueId val="{00000006-D09D-4669-AAE7-BA22EB458689}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1509,7 +1509,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1883-4677-869D-66D9E0F8764E}"/>
+              <c16:uniqueId val="{00000000-CB2F-40EE-8519-AEAA40DD121C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1629,7 +1629,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-FF76-4F65-B10D-2059C4C0A570}"/>
+                <c16:uniqueId val="{00000001-F242-417B-94EA-387008282385}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1639,7 +1639,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-FF76-4F65-B10D-2059C4C0A570}"/>
+                <c16:uniqueId val="{00000003-F242-417B-94EA-387008282385}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1649,7 +1649,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-FF76-4F65-B10D-2059C4C0A570}"/>
+                <c16:uniqueId val="{00000005-F242-417B-94EA-387008282385}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1659,7 +1659,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-FF76-4F65-B10D-2059C4C0A570}"/>
+                <c16:uniqueId val="{00000007-F242-417B-94EA-387008282385}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1669,7 +1669,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-FF76-4F65-B10D-2059C4C0A570}"/>
+                <c16:uniqueId val="{00000009-F242-417B-94EA-387008282385}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1679,7 +1679,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-FF76-4F65-B10D-2059C4C0A570}"/>
+                <c16:uniqueId val="{0000000B-F242-417B-94EA-387008282385}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1753,7 +1753,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-FF76-4F65-B10D-2059C4C0A570}"/>
+              <c16:uniqueId val="{0000000C-F242-417B-94EA-387008282385}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-5yxkm8zf\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-do642wo4\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9722442A-3029-4AA0-A9CC-E13006E31BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F13E13-D452-4A51-A730-4D2F0F2A512C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -1054,7 +1054,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-16C4-4621-B345-9C2E5DBE8B8B}"/>
+              <c16:uniqueId val="{00000000-F486-45EB-9AD7-289962AC11F6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1154,7 +1154,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-16C4-4621-B345-9C2E5DBE8B8B}"/>
+              <c16:uniqueId val="{00000001-F486-45EB-9AD7-289962AC11F6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1278,7 +1278,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-D09D-4669-AAE7-BA22EB458689}"/>
+                <c16:uniqueId val="{00000001-0A9C-4952-A7EE-E10006992F45}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1288,7 +1288,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-D09D-4669-AAE7-BA22EB458689}"/>
+                <c16:uniqueId val="{00000003-0A9C-4952-A7EE-E10006992F45}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1298,7 +1298,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-D09D-4669-AAE7-BA22EB458689}"/>
+                <c16:uniqueId val="{00000005-0A9C-4952-A7EE-E10006992F45}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1354,7 +1354,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-D09D-4669-AAE7-BA22EB458689}"/>
+              <c16:uniqueId val="{00000006-0A9C-4952-A7EE-E10006992F45}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1509,7 +1509,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CB2F-40EE-8519-AEAA40DD121C}"/>
+              <c16:uniqueId val="{00000000-769A-4499-9457-CDFC8292A9AC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1629,7 +1629,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F242-417B-94EA-387008282385}"/>
+                <c16:uniqueId val="{00000001-9E7E-4F9C-96CF-9A63D640BE49}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1639,7 +1639,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F242-417B-94EA-387008282385}"/>
+                <c16:uniqueId val="{00000003-9E7E-4F9C-96CF-9A63D640BE49}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1649,7 +1649,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F242-417B-94EA-387008282385}"/>
+                <c16:uniqueId val="{00000005-9E7E-4F9C-96CF-9A63D640BE49}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1659,7 +1659,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-F242-417B-94EA-387008282385}"/>
+                <c16:uniqueId val="{00000007-9E7E-4F9C-96CF-9A63D640BE49}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1669,7 +1669,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-F242-417B-94EA-387008282385}"/>
+                <c16:uniqueId val="{00000009-9E7E-4F9C-96CF-9A63D640BE49}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1679,7 +1679,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-F242-417B-94EA-387008282385}"/>
+                <c16:uniqueId val="{0000000B-9E7E-4F9C-96CF-9A63D640BE49}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1753,7 +1753,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-F242-417B-94EA-387008282385}"/>
+              <c16:uniqueId val="{0000000C-9E7E-4F9C-96CF-9A63D640BE49}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5440,7 +5440,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="7">
-        <f>价格计算依据!D4+价格计算依据!D5</f>
+        <f>SUM(价格计算依据!D4:D5)</f>
         <v>183.96</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -5500,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="7">
-        <f>价格计算依据!D6+价格计算依据!D7</f>
+        <f>SUM(价格计算依据!D6:D7)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -5560,7 +5560,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="7">
-        <f>价格计算依据!D8+价格计算依据!D9+价格计算依据!D10+价格计算依据!D11+价格计算依据!D12+价格计算依据!D13</f>
+        <f>SUM(价格计算依据!D8:D13)</f>
         <v>486.10700000000008</v>
       </c>
       <c r="H8" s="4" t="s">
@@ -5590,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="10">
-        <f>价格计算依据!D14+价格计算依据!D15</f>
+        <f>SUM(价格计算依据!D14:D15)</f>
         <v>90.447000000000003</v>
       </c>
       <c r="H9" s="2" t="s">

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-do642wo4\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-jluf97rf\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F13E13-D452-4A51-A730-4D2F0F2A512C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C591C8-8E48-4BDC-A20B-B37CEFF977AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1054,7 +1054,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F486-45EB-9AD7-289962AC11F6}"/>
+              <c16:uniqueId val="{00000000-9F10-4F05-B44D-B3AD40EAA4F0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1154,7 +1154,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F486-45EB-9AD7-289962AC11F6}"/>
+              <c16:uniqueId val="{00000001-9F10-4F05-B44D-B3AD40EAA4F0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1278,7 +1278,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-0A9C-4952-A7EE-E10006992F45}"/>
+                <c16:uniqueId val="{00000001-5BEA-4539-9C04-57EC6CABCDC6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1288,7 +1288,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-0A9C-4952-A7EE-E10006992F45}"/>
+                <c16:uniqueId val="{00000003-5BEA-4539-9C04-57EC6CABCDC6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1298,7 +1298,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-0A9C-4952-A7EE-E10006992F45}"/>
+                <c16:uniqueId val="{00000005-5BEA-4539-9C04-57EC6CABCDC6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1354,7 +1354,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-0A9C-4952-A7EE-E10006992F45}"/>
+              <c16:uniqueId val="{00000006-5BEA-4539-9C04-57EC6CABCDC6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1509,7 +1509,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-769A-4499-9457-CDFC8292A9AC}"/>
+              <c16:uniqueId val="{00000000-0E12-49F6-A2F8-D7410FD3582B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1629,7 +1629,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-9E7E-4F9C-96CF-9A63D640BE49}"/>
+                <c16:uniqueId val="{00000001-6D5C-463D-A717-0F10EFDB101F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1639,7 +1639,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-9E7E-4F9C-96CF-9A63D640BE49}"/>
+                <c16:uniqueId val="{00000003-6D5C-463D-A717-0F10EFDB101F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1649,7 +1649,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-9E7E-4F9C-96CF-9A63D640BE49}"/>
+                <c16:uniqueId val="{00000005-6D5C-463D-A717-0F10EFDB101F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1659,7 +1659,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-9E7E-4F9C-96CF-9A63D640BE49}"/>
+                <c16:uniqueId val="{00000007-6D5C-463D-A717-0F10EFDB101F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1669,7 +1669,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-9E7E-4F9C-96CF-9A63D640BE49}"/>
+                <c16:uniqueId val="{00000009-6D5C-463D-A717-0F10EFDB101F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1679,7 +1679,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-9E7E-4F9C-96CF-9A63D640BE49}"/>
+                <c16:uniqueId val="{0000000B-6D5C-463D-A717-0F10EFDB101F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1753,7 +1753,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-9E7E-4F9C-96CF-9A63D640BE49}"/>
+              <c16:uniqueId val="{0000000C-6D5C-463D-A717-0F10EFDB101F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-jluf97rf\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-4z_oecii\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C591C8-8E48-4BDC-A20B-B37CEFF977AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7C43ED-3D5A-41B2-A9BE-021746B01419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -1054,7 +1054,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9F10-4F05-B44D-B3AD40EAA4F0}"/>
+              <c16:uniqueId val="{00000000-A7E3-49A1-B1E2-46CFEC0C0885}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1154,7 +1154,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9F10-4F05-B44D-B3AD40EAA4F0}"/>
+              <c16:uniqueId val="{00000001-A7E3-49A1-B1E2-46CFEC0C0885}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1278,7 +1278,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-5BEA-4539-9C04-57EC6CABCDC6}"/>
+                <c16:uniqueId val="{00000001-898F-4145-B4A1-7CACADD3D107}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1288,7 +1288,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5BEA-4539-9C04-57EC6CABCDC6}"/>
+                <c16:uniqueId val="{00000003-898F-4145-B4A1-7CACADD3D107}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1298,7 +1298,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5BEA-4539-9C04-57EC6CABCDC6}"/>
+                <c16:uniqueId val="{00000005-898F-4145-B4A1-7CACADD3D107}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1354,7 +1354,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-5BEA-4539-9C04-57EC6CABCDC6}"/>
+              <c16:uniqueId val="{00000006-898F-4145-B4A1-7CACADD3D107}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1509,7 +1509,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0E12-49F6-A2F8-D7410FD3582B}"/>
+              <c16:uniqueId val="{00000000-C1DC-4E4E-9F1A-F9B149171AAA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1629,7 +1629,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-6D5C-463D-A717-0F10EFDB101F}"/>
+                <c16:uniqueId val="{00000001-C55C-4DBD-9927-A3FFA90C1946}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1639,7 +1639,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-6D5C-463D-A717-0F10EFDB101F}"/>
+                <c16:uniqueId val="{00000003-C55C-4DBD-9927-A3FFA90C1946}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1649,7 +1649,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-6D5C-463D-A717-0F10EFDB101F}"/>
+                <c16:uniqueId val="{00000005-C55C-4DBD-9927-A3FFA90C1946}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1659,7 +1659,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-6D5C-463D-A717-0F10EFDB101F}"/>
+                <c16:uniqueId val="{00000007-C55C-4DBD-9927-A3FFA90C1946}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1669,7 +1669,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-6D5C-463D-A717-0F10EFDB101F}"/>
+                <c16:uniqueId val="{00000009-C55C-4DBD-9927-A3FFA90C1946}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1679,7 +1679,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-6D5C-463D-A717-0F10EFDB101F}"/>
+                <c16:uniqueId val="{0000000B-C55C-4DBD-9927-A3FFA90C1946}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1753,7 +1753,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-6D5C-463D-A717-0F10EFDB101F}"/>
+              <c16:uniqueId val="{0000000C-C55C-4DBD-9927-A3FFA90C1946}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-4z_oecii\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-gq0eyj71\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7C43ED-3D5A-41B2-A9BE-021746B01419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB7C810-99EA-4F77-B89E-7706E07D05A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1054,7 +1054,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A7E3-49A1-B1E2-46CFEC0C0885}"/>
+              <c16:uniqueId val="{00000000-13D5-47A0-913F-4BFB5B98EE57}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1154,7 +1154,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A7E3-49A1-B1E2-46CFEC0C0885}"/>
+              <c16:uniqueId val="{00000001-13D5-47A0-913F-4BFB5B98EE57}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1278,7 +1278,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-898F-4145-B4A1-7CACADD3D107}"/>
+                <c16:uniqueId val="{00000001-F0C0-42C1-9FBF-277B22BE56CB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1288,7 +1288,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-898F-4145-B4A1-7CACADD3D107}"/>
+                <c16:uniqueId val="{00000003-F0C0-42C1-9FBF-277B22BE56CB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1298,7 +1298,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-898F-4145-B4A1-7CACADD3D107}"/>
+                <c16:uniqueId val="{00000005-F0C0-42C1-9FBF-277B22BE56CB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1354,7 +1354,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-898F-4145-B4A1-7CACADD3D107}"/>
+              <c16:uniqueId val="{00000006-F0C0-42C1-9FBF-277B22BE56CB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1509,7 +1509,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C1DC-4E4E-9F1A-F9B149171AAA}"/>
+              <c16:uniqueId val="{00000000-F8A5-44DC-A2C6-1877035D23B5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1629,7 +1629,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-C55C-4DBD-9927-A3FFA90C1946}"/>
+                <c16:uniqueId val="{00000001-4552-4868-B44B-A59E79075424}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1639,7 +1639,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-C55C-4DBD-9927-A3FFA90C1946}"/>
+                <c16:uniqueId val="{00000003-4552-4868-B44B-A59E79075424}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1649,7 +1649,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-C55C-4DBD-9927-A3FFA90C1946}"/>
+                <c16:uniqueId val="{00000005-4552-4868-B44B-A59E79075424}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1659,7 +1659,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-C55C-4DBD-9927-A3FFA90C1946}"/>
+                <c16:uniqueId val="{00000007-4552-4868-B44B-A59E79075424}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1669,7 +1669,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-C55C-4DBD-9927-A3FFA90C1946}"/>
+                <c16:uniqueId val="{00000009-4552-4868-B44B-A59E79075424}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1679,7 +1679,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-C55C-4DBD-9927-A3FFA90C1946}"/>
+                <c16:uniqueId val="{0000000B-4552-4868-B44B-A59E79075424}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1753,7 +1753,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-C55C-4DBD-9927-A3FFA90C1946}"/>
+              <c16:uniqueId val="{0000000C-4552-4868-B44B-A59E79075424}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/02_虚拟机利用率与规格优化.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-gq0eyj71\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-9n18lti6\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB7C810-99EA-4F77-B89E-7706E07D05A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC6B29A-2B8E-470B-ABF5-9DA93F0D7F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1054,7 +1054,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-13D5-47A0-913F-4BFB5B98EE57}"/>
+              <c16:uniqueId val="{00000000-A4A5-432D-BA85-79B0C8A82E69}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1154,7 +1154,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-13D5-47A0-913F-4BFB5B98EE57}"/>
+              <c16:uniqueId val="{00000001-A4A5-432D-BA85-79B0C8A82E69}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1278,7 +1278,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F0C0-42C1-9FBF-277B22BE56CB}"/>
+                <c16:uniqueId val="{00000001-EB14-4C47-ADA2-824949EBA436}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1288,7 +1288,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F0C0-42C1-9FBF-277B22BE56CB}"/>
+                <c16:uniqueId val="{00000003-EB14-4C47-ADA2-824949EBA436}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1298,7 +1298,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F0C0-42C1-9FBF-277B22BE56CB}"/>
+                <c16:uniqueId val="{00000005-EB14-4C47-ADA2-824949EBA436}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1354,7 +1354,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-F0C0-42C1-9FBF-277B22BE56CB}"/>
+              <c16:uniqueId val="{00000006-EB14-4C47-ADA2-824949EBA436}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1509,7 +1509,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F8A5-44DC-A2C6-1877035D23B5}"/>
+              <c16:uniqueId val="{00000000-3A7A-43B7-9DBA-FFA30A4BBA9C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1629,7 +1629,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-4552-4868-B44B-A59E79075424}"/>
+                <c16:uniqueId val="{00000001-CE43-4A58-AF7D-687D65A3DB84}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1639,7 +1639,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-4552-4868-B44B-A59E79075424}"/>
+                <c16:uniqueId val="{00000003-CE43-4A58-AF7D-687D65A3DB84}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1649,7 +1649,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-4552-4868-B44B-A59E79075424}"/>
+                <c16:uniqueId val="{00000005-CE43-4A58-AF7D-687D65A3DB84}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1659,7 +1659,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-4552-4868-B44B-A59E79075424}"/>
+                <c16:uniqueId val="{00000007-CE43-4A58-AF7D-687D65A3DB84}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1669,7 +1669,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-4552-4868-B44B-A59E79075424}"/>
+                <c16:uniqueId val="{00000009-CE43-4A58-AF7D-687D65A3DB84}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1679,7 +1679,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-4552-4868-B44B-A59E79075424}"/>
+                <c16:uniqueId val="{0000000B-CE43-4A58-AF7D-687D65A3DB84}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1753,7 +1753,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-4552-4868-B44B-A59E79075424}"/>
+              <c16:uniqueId val="{0000000C-CE43-4A58-AF7D-687D65A3DB84}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
